--- a/Manuscript/stat_tables/together.xlsx
+++ b/Manuscript/stat_tables/together.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ggraham/Desktop/multiome_poa/Manuscript/stat_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16513E84-69ED-3040-8C4F-9FADA74E3D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDE1DF0-6E9D-7A47-8392-C7AE44D05462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41640" yWindow="1980" windowWidth="27240" windowHeight="16440" activeTab="8" xr2:uid="{556DCCEF-41EF-0249-BF61-3303BB8799AD}"/>
+    <workbookView xWindow="41640" yWindow="1980" windowWidth="27240" windowHeight="16440" xr2:uid="{556DCCEF-41EF-0249-BF61-3303BB8799AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig. 1B,C" sheetId="3" r:id="rId1"/>
-    <sheet name="Fig.2 C,B Enrichment" sheetId="9" r:id="rId2"/>
-    <sheet name="Fig. 3A,B 4G,H" sheetId="1" r:id="rId3"/>
-    <sheet name="Fig. 4I" sheetId="2" r:id="rId4"/>
-    <sheet name="Fig. 5D" sheetId="4" r:id="rId5"/>
-    <sheet name="Fig. 5E-G, 6A-C, S10D,E" sheetId="5" r:id="rId6"/>
+    <sheet name="Fig. 3A,B, 4C,D, 5 A-C, S10A-E" sheetId="1" r:id="rId2"/>
+    <sheet name="Fig.3 C,D Enrichment" sheetId="9" r:id="rId3"/>
+    <sheet name="Fig. 4F" sheetId="2" r:id="rId4"/>
+    <sheet name="Fig. 5E, 6A-C, S10D,E" sheetId="5" r:id="rId5"/>
+    <sheet name="Fig. 5F,G" sheetId="11" r:id="rId6"/>
     <sheet name="Fig. 6 D-F" sheetId="8" r:id="rId7"/>
     <sheet name="Fig. S1A-F" sheetId="6" r:id="rId8"/>
     <sheet name="Fig. S6A, B" sheetId="10" r:id="rId9"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="170">
   <si>
     <t>model</t>
   </si>
@@ -89,9 +89,6 @@
     <t>3A</t>
   </si>
   <si>
-    <t>none</t>
-  </si>
-  <si>
     <t>z.ratio</t>
   </si>
   <si>
@@ -155,9 +152,6 @@
     <t>lm(neuron_differentiation~Status)</t>
   </si>
   <si>
-    <t>4I</t>
-  </si>
-  <si>
     <t>t.ratio</t>
   </si>
   <si>
@@ -293,108 +287,9 @@
     <t>anova_statistic</t>
   </si>
   <si>
-    <t>anova_p.value_Phase</t>
-  </si>
-  <si>
-    <t>anova_df_Phase</t>
-  </si>
-  <si>
-    <t>anova_chisq_Phase</t>
-  </si>
-  <si>
-    <t>anova_p.value_nCount_RNA</t>
-  </si>
-  <si>
-    <t>anova_df_nCountRNA</t>
-  </si>
-  <si>
-    <t>anova_chisq_nCountRNA</t>
-  </si>
-  <si>
-    <t>anova_p.value_ecm_deg_positive</t>
-  </si>
-  <si>
-    <t>anova_df_ecm_deg_positive</t>
-  </si>
-  <si>
-    <t>anova_chisq_ecm_deg_positive</t>
-  </si>
-  <si>
-    <t>anova_p.value_phase:ecm_deg_positive</t>
-  </si>
-  <si>
-    <t>anova_df_phase:ecm_deg_positive</t>
-  </si>
-  <si>
-    <t>anova_chisq_phase:ecm_deg_positive</t>
-  </si>
-  <si>
     <t>pairwise_statistic</t>
   </si>
   <si>
-    <t>pairwise_p.value_correction</t>
-  </si>
-  <si>
-    <t>ecm_deg_pos_m_i_p.value</t>
-  </si>
-  <si>
-    <t>ecm_deg_pos_m_f_p.value</t>
-  </si>
-  <si>
-    <t>ecm_deg_pos_i_f_p.value</t>
-  </si>
-  <si>
-    <t>ecm_deg_pos_m_i_statistic</t>
-  </si>
-  <si>
-    <t>ecm_deg_pos_m_f_statistic</t>
-  </si>
-  <si>
-    <t>ecm_deg_pos_i_f_statistic</t>
-  </si>
-  <si>
-    <t>ecm_deg_pos_m_i_df</t>
-  </si>
-  <si>
-    <t>ecm_deg_pos_m_f_df</t>
-  </si>
-  <si>
-    <t>ecm_deg_pos_i_f_df</t>
-  </si>
-  <si>
-    <t>ecm_deg_neg_m_i_p.value</t>
-  </si>
-  <si>
-    <t>ecm_deg_neg_m_f_p.value</t>
-  </si>
-  <si>
-    <t>ecm_deg_neg_i_f_p.value</t>
-  </si>
-  <si>
-    <t>ecm_deg_neg_m_i_statistic</t>
-  </si>
-  <si>
-    <t>ecm_deg_neg_m_f_statistic</t>
-  </si>
-  <si>
-    <t>ecm_deg_neg_i_f_statistic</t>
-  </si>
-  <si>
-    <t>ecm_deg_neg_m_i_df</t>
-  </si>
-  <si>
-    <t>ecm_deg_neg_m_f_df</t>
-  </si>
-  <si>
-    <t>ecm_deg_neg_i_f_df</t>
-  </si>
-  <si>
-    <t>lmer(CytoTRACE~nCount_RNA+Phase*ecm_deg_positive +(1|individual))</t>
-  </si>
-  <si>
-    <t>5D</t>
-  </si>
-  <si>
     <t>Chisq</t>
   </si>
   <si>
@@ -599,15 +494,9 @@
     <t>Chi-squared test for given probabilities</t>
   </si>
   <si>
-    <t>data:  degs_clust$n</t>
-  </si>
-  <si>
     <t>X-squared = 410.39, df = 25, p-value &lt; 2.2e-16</t>
   </si>
   <si>
-    <t>data:  dars_clust$n</t>
-  </si>
-  <si>
     <t>X-squared = 42.943, df = 14, p-value = 8.747e-05</t>
   </si>
   <si>
@@ -651,25 +540,37 @@
   </si>
   <si>
     <t>anova_q.value</t>
+  </si>
+  <si>
+    <t>S10B Right</t>
+  </si>
+  <si>
+    <t>S10A Right</t>
+  </si>
+  <si>
+    <t>S10E Middle</t>
+  </si>
+  <si>
+    <t>S10C Right</t>
+  </si>
+  <si>
+    <t>S10D Middle</t>
+  </si>
+  <si>
+    <t>4F</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Lucida Grande"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -698,13 +599,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1056,25 +955,25 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" t="s">
         <v>38</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>39</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>40</v>
-      </c>
-      <c r="J1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" t="s">
-        <v>42</v>
       </c>
       <c r="L1" t="s">
         <v>4</v>
@@ -1098,102 +997,102 @@
         <v>10</v>
       </c>
       <c r="S1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U1" t="s">
         <v>43</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>44</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>45</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>46</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>47</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>48</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>49</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>50</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>51</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>52</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>53</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>54</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>55</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>56</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>57</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>58</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>59</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>60</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>61</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>62</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>63</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>64</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>65</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>66</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>67</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>68</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>69</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>70</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>4.5786595547978502E-2</v>
@@ -1202,28 +1101,28 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>2.47918090658158</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M2">
         <v>0.89890002766070498</v>
@@ -1232,16 +1131,16 @@
         <v>-0.128402952074223</v>
       </c>
       <c r="O2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="S2">
         <v>1.3786529992469701E-2</v>
@@ -1336,10 +1235,10 @@
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>9.8154066897584102E-4</v>
@@ -1348,13 +1247,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>6.8310944024577598</v>
       </c>
       <c r="G3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H3">
         <v>1.66323709376501E-2</v>
@@ -1369,7 +1268,7 @@
         <v>6.9702365136231803</v>
       </c>
       <c r="L3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M3">
         <v>1.70086834579838E-2</v>
@@ -1378,16 +1277,16 @@
         <v>2.6295174446340499</v>
       </c>
       <c r="O3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="S3">
         <v>0.249167819424186</v>
@@ -1408,10 +1307,10 @@
         <v>-0.40302538558694601</v>
       </c>
       <c r="Y3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Z3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AA3">
         <v>0.106751612995915</v>
@@ -1432,10 +1331,10 @@
         <v>-1.58271438573012</v>
       </c>
       <c r="AG3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AH3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AI3">
         <v>1.48571574264057E-2</v>
@@ -1450,10 +1349,10 @@
         <v>1.6446934216776601</v>
       </c>
       <c r="AM3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AN3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AO3">
         <v>0.857271091249172</v>
@@ -1462,10 +1361,10 @@
         <v>0.18244692529517501</v>
       </c>
       <c r="AQ3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AR3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AS3">
         <v>0.20543576198714</v>
@@ -1474,18 +1373,18 @@
         <v>-1.31373024230237</v>
       </c>
       <c r="AU3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AV3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C4" s="1">
         <v>4.9384071351100505E-7</v>
@@ -1494,28 +1393,28 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>20.348934169379099</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M4" s="1">
         <v>2.8733786029515101E-7</v>
@@ -1524,16 +1423,16 @@
         <v>-7.7125798600322799</v>
       </c>
       <c r="O4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="S4">
         <v>0.18871145927830699</v>
@@ -1554,10 +1453,10 @@
         <v>2.46038331250235</v>
       </c>
       <c r="Y4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Z4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AA4">
         <v>6.9240140926171301E-3</v>
@@ -1578,10 +1477,10 @@
         <v>3.3692809407494599</v>
       </c>
       <c r="AG4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AH4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AI4">
         <v>1.4877565544141799E-3</v>
@@ -1596,10 +1495,10 @@
         <v>-0.50612996487642803</v>
       </c>
       <c r="AM4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AN4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AO4">
         <v>0.54339382438166905</v>
@@ -1608,10 +1507,10 @@
         <v>0.61880431223457799</v>
       </c>
       <c r="AQ4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AR4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AS4">
         <v>0.31500417034442801</v>
@@ -1620,18 +1519,18 @@
         <v>1.0320576980612499</v>
       </c>
       <c r="AU4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AV4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5" s="1">
         <v>2.7024864879974299E-7</v>
@@ -1640,28 +1539,28 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>21.973385347999798</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M5" s="1">
         <v>7.99626291748166E-7</v>
@@ -1670,16 +1569,16 @@
         <v>7.1824017131322702</v>
       </c>
       <c r="O5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="S5">
         <v>0.17885683858281101</v>
@@ -1700,10 +1599,10 @@
         <v>-2.5388169039222901</v>
       </c>
       <c r="Y5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Z5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AA5">
         <v>9.0569445980018294E-3</v>
@@ -1724,10 +1623,10 @@
         <v>-3.4693872970859698</v>
       </c>
       <c r="AG5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AH5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AI5">
         <v>1.89114354753929E-3</v>
@@ -1742,10 +1641,10 @@
         <v>-4.3234066940497398</v>
       </c>
       <c r="AM5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AN5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AO5">
         <v>3.0449522192802501E-4</v>
@@ -1754,10 +1653,10 @@
         <v>-4.40463141115635</v>
       </c>
       <c r="AQ5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AR5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AS5">
         <v>0.39272129134886302</v>
@@ -1766,18 +1665,18 @@
         <v>-0.87458462750469301</v>
       </c>
       <c r="AU5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AV5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>1.7123024334253702E-2</v>
@@ -1786,28 +1685,28 @@
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>3.1267846252742899</v>
       </c>
       <c r="G6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M6">
         <v>0.69129741739675599</v>
@@ -1816,16 +1715,16 @@
         <v>0.401923294652833</v>
       </c>
       <c r="O6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="S6">
         <v>6.9075240015484003E-3</v>
@@ -1920,10 +1819,10 @@
     </row>
     <row r="7" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7">
         <v>4.5786595547978502E-2</v>
@@ -1932,28 +1831,28 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>2.47918090658158</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M7">
         <v>0.89890002766070498</v>
@@ -1962,16 +1861,16 @@
         <v>-0.128402952074223</v>
       </c>
       <c r="O7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="S7">
         <v>1.3786529992469701E-2</v>
@@ -2085,66 +1984,66 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E1" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="F1" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="G1" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="H1" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="I1" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="J1" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="K1" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="L1" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="M1" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="N1" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="O1" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="P1" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="Q1" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="R1" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="S1" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="C2" s="1">
         <v>2.2E-16</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="E2">
         <v>686.16</v>
@@ -2153,10 +2052,10 @@
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <v>5.0000000000000001E-4</v>
@@ -2165,10 +2064,10 @@
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M2">
         <v>0.8175</v>
@@ -2198,39 +2097,586 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72E959D-7FB4-F748-AD7C-99DDE058A0B2}">
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="45.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>9.5620000000000004E-4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2">
+        <v>13.904999999999999</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="I2">
+        <v>-3.0819999999999999</v>
+      </c>
+      <c r="J2">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="K2">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="L2">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="M2">
+        <v>4.7199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>1.8030000000000001E-2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3">
+        <v>8.0312999999999999</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3">
+        <v>0.50960000000000005</v>
+      </c>
+      <c r="I3">
+        <v>-0.65900000000000003</v>
+      </c>
+      <c r="J3">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="K3">
+        <v>7.4499999999999997E-2</v>
+      </c>
+      <c r="L3">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="M3">
+        <v>7.3300000000000004E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4.9399999999999999E-3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4">
+        <v>10.621</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4">
+        <v>1.8E-3</v>
+      </c>
+      <c r="I4">
+        <v>3.125</v>
+      </c>
+      <c r="J4">
+        <v>0.35630000000000001</v>
+      </c>
+      <c r="K4">
+        <v>0.92200000000000004</v>
+      </c>
+      <c r="L4">
+        <v>2.12E-2</v>
+      </c>
+      <c r="M4">
+        <v>-2.3039999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.3099999999999999E-7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5">
+        <v>30.564</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="I5">
+        <v>-2.1419999999999999</v>
+      </c>
+      <c r="J5">
+        <v>1.9E-3</v>
+      </c>
+      <c r="K5">
+        <v>3.1070000000000002</v>
+      </c>
+      <c r="L5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5">
+        <v>5.4779999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>4.6499999999999996E-3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6">
+        <v>10.742000000000001</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>0.50260000000000005</v>
+      </c>
+      <c r="I6">
+        <v>-0.67</v>
+      </c>
+      <c r="J6">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="K6">
+        <v>-2.673</v>
+      </c>
+      <c r="L6">
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="M6">
+        <v>-2.21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1.917E-6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7">
+        <v>26.33</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>2.64E-2</v>
+      </c>
+      <c r="I7">
+        <v>-2.2200000000000002</v>
+      </c>
+      <c r="J7">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="K7">
+        <v>2.6230000000000002</v>
+      </c>
+      <c r="L7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7">
+        <v>4.7720000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8">
+        <v>2.409E-2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8">
+        <v>7.4523000000000001</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>0.62890000000000001</v>
+      </c>
+      <c r="I8">
+        <v>-0.48299999999999998</v>
+      </c>
+      <c r="J8">
+        <v>1.49E-2</v>
+      </c>
+      <c r="K8">
+        <v>-2.4359999999999999</v>
+      </c>
+      <c r="L8">
+        <v>4.65E-2</v>
+      </c>
+      <c r="M8">
+        <v>-1.9910000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9">
+        <v>4.0030000000000003E-4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9">
+        <v>15.647</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>0.41020000000000001</v>
+      </c>
+      <c r="I9">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="J9">
+        <v>7.7999999999999996E-3</v>
+      </c>
+      <c r="K9">
+        <v>-2.6589999999999998</v>
+      </c>
+      <c r="L9">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="M9">
+        <v>-3.4569999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10">
+        <v>1.8159999999999999E-2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10">
+        <v>8.0165000000000006</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>0.48730000000000001</v>
+      </c>
+      <c r="I10">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="J10">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="K10">
+        <v>2.6930000000000001</v>
+      </c>
+      <c r="L10">
+        <v>4.7199999999999999E-2</v>
+      </c>
+      <c r="M10">
+        <v>1.984</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11">
+        <v>7.3709999999999999E-3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11">
+        <v>9.8204999999999991</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>0.15759999999999999</v>
+      </c>
+      <c r="I11">
+        <v>1.413</v>
+      </c>
+      <c r="J11">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="K11">
+        <v>2.819</v>
+      </c>
+      <c r="L11">
+        <v>0.11360000000000001</v>
+      </c>
+      <c r="M11">
+        <v>1.5820000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="1">
+        <v>8.5619999999999997E-5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12">
+        <v>18.731000000000002</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>0.55589999999999995</v>
+      </c>
+      <c r="I12">
+        <v>-0.58899999999999997</v>
+      </c>
+      <c r="J12">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="K12">
+        <v>-3.508</v>
+      </c>
+      <c r="L12">
+        <v>1.9E-3</v>
+      </c>
+      <c r="M12">
+        <v>-3.1040000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13">
+        <v>0.2767</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13">
+        <v>2.5699000000000001</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="I13">
+        <v>-0.65300000000000002</v>
+      </c>
+      <c r="J13">
+        <v>0.12670000000000001</v>
+      </c>
+      <c r="K13">
+        <v>-1.5269999999999999</v>
+      </c>
+      <c r="L13">
+        <v>0.372</v>
+      </c>
+      <c r="M13">
+        <v>-0.89300000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50DD0666-3A1E-C247-AAEA-CBCAA6278EC1}">
   <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="B1" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="C1" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="D1" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="E1" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="F1" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="G1" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="H1" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2256,7 +2702,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -2280,12 +2726,12 @@
         <v>1.03488319896057E-21</v>
       </c>
       <c r="L3" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -2311,7 +2757,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -2334,13 +2780,10 @@
       <c r="H5">
         <v>0.53974168568127801</v>
       </c>
-      <c r="K5" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -2364,12 +2807,12 @@
         <v>4.4453149384886703E-2</v>
       </c>
       <c r="K6" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -2395,7 +2838,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -2421,7 +2864,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -2447,7 +2890,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -2473,7 +2916,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B11">
         <v>9</v>
@@ -2499,7 +2942,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -2525,7 +2968,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B13">
         <v>11</v>
@@ -2551,7 +2994,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B14">
         <v>12</v>
@@ -2577,7 +3020,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B15">
         <v>13</v>
@@ -2603,7 +3046,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -2629,7 +3072,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -2655,7 +3098,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -2681,7 +3124,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -2707,7 +3150,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -2733,7 +3176,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -2759,7 +3202,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -2785,7 +3228,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B23">
         <v>22</v>
@@ -2811,7 +3254,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B24">
         <v>23</v>
@@ -2837,7 +3280,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -2863,7 +3306,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B26">
         <v>25</v>
@@ -2889,7 +3332,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="B27">
         <v>26</v>
@@ -2915,7 +3358,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2941,7 +3384,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -2967,7 +3410,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -2991,12 +3434,12 @@
         <v>2.7260169568030498E-2</v>
       </c>
       <c r="L31" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -3022,7 +3465,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B33">
         <v>5</v>
@@ -3045,13 +3488,10 @@
       <c r="H33">
         <v>0.296246830769828</v>
       </c>
-      <c r="K33" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B34">
         <v>6</v>
@@ -3075,12 +3515,12 @@
         <v>0.80392982937769997</v>
       </c>
       <c r="K34" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B35">
         <v>11</v>
@@ -3106,7 +3546,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B36">
         <v>12</v>
@@ -3132,7 +3572,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B37">
         <v>13</v>
@@ -3158,7 +3598,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B38">
         <v>15</v>
@@ -3184,7 +3624,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B39">
         <v>17</v>
@@ -3210,7 +3650,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B40">
         <v>19</v>
@@ -3236,7 +3676,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B41">
         <v>20</v>
@@ -3262,7 +3702,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B42">
         <v>22</v>
@@ -3288,7 +3728,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B43">
         <v>23</v>
@@ -3314,535 +3754,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72E959D-7FB4-F748-AD7C-99DDE058A0B2}">
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>9.5620000000000004E-4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E2">
-        <v>13.904999999999999</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="I2">
-        <v>-3.0819999999999999</v>
-      </c>
-      <c r="J2">
-        <v>0.90700000000000003</v>
-      </c>
-      <c r="K2">
-        <v>0.11700000000000001</v>
-      </c>
-      <c r="L2">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="M2">
-        <v>4.7199999999999999E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3">
-        <v>1.8030000000000001E-2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E3">
-        <v>8.0312999999999999</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>0.50960000000000005</v>
-      </c>
-      <c r="I3">
-        <v>-0.65900000000000003</v>
-      </c>
-      <c r="J3">
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="K3">
-        <v>7.4499999999999997E-2</v>
-      </c>
-      <c r="L3">
-        <v>4.4400000000000002E-2</v>
-      </c>
-      <c r="M3">
-        <v>7.3300000000000004E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1">
-        <v>4.9399999999999999E-3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4">
-        <v>10.621</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4">
-        <v>1.8E-3</v>
-      </c>
-      <c r="I4">
-        <v>3.125</v>
-      </c>
-      <c r="J4">
-        <v>0.35630000000000001</v>
-      </c>
-      <c r="K4">
-        <v>0.92200000000000004</v>
-      </c>
-      <c r="L4">
-        <v>2.12E-2</v>
-      </c>
-      <c r="M4">
-        <v>-2.3039999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2.3099999999999999E-7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5">
-        <v>30.564</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5">
-        <v>3.2199999999999999E-2</v>
-      </c>
-      <c r="I5">
-        <v>-2.1419999999999999</v>
-      </c>
-      <c r="J5">
-        <v>1.9E-3</v>
-      </c>
-      <c r="K5">
-        <v>3.1070000000000002</v>
-      </c>
-      <c r="L5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5">
-        <v>5.4779999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6">
-        <v>4.6499999999999996E-3</v>
-      </c>
-      <c r="D6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6">
-        <v>10.742000000000001</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>0.50260000000000005</v>
-      </c>
-      <c r="I6">
-        <v>-0.67</v>
-      </c>
-      <c r="J6">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="K6">
-        <v>-2.673</v>
-      </c>
-      <c r="L6">
-        <v>2.7099999999999999E-2</v>
-      </c>
-      <c r="M6">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1.917E-6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E7">
-        <v>26.33</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7">
-        <v>2.64E-2</v>
-      </c>
-      <c r="I7">
-        <v>-2.2200000000000002</v>
-      </c>
-      <c r="J7">
-        <v>8.6999999999999994E-3</v>
-      </c>
-      <c r="K7">
-        <v>2.6230000000000002</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7">
-        <v>4.7720000000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8">
-        <v>2.409E-2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E8">
-        <v>7.4523000000000001</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8">
-        <v>0.62890000000000001</v>
-      </c>
-      <c r="I8">
-        <v>-0.48299999999999998</v>
-      </c>
-      <c r="J8">
-        <v>1.49E-2</v>
-      </c>
-      <c r="K8">
-        <v>-2.4359999999999999</v>
-      </c>
-      <c r="L8">
-        <v>4.65E-2</v>
-      </c>
-      <c r="M8">
-        <v>-1.9910000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9">
-        <v>4.0030000000000003E-4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E9">
-        <v>15.647</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9">
-        <v>0.41020000000000001</v>
-      </c>
-      <c r="I9">
-        <v>0.82299999999999995</v>
-      </c>
-      <c r="J9">
-        <v>7.7999999999999996E-3</v>
-      </c>
-      <c r="K9">
-        <v>-2.6589999999999998</v>
-      </c>
-      <c r="L9">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="M9">
-        <v>-3.4569999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10">
-        <v>1.8159999999999999E-2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10">
-        <v>8.0165000000000006</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10">
-        <v>0.48730000000000001</v>
-      </c>
-      <c r="I10">
-        <v>0.69499999999999995</v>
-      </c>
-      <c r="J10">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="K10">
-        <v>2.6930000000000001</v>
-      </c>
-      <c r="L10">
-        <v>4.7199999999999999E-2</v>
-      </c>
-      <c r="M10">
-        <v>1.984</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11">
-        <v>7.3709999999999999E-3</v>
-      </c>
-      <c r="D11" t="s">
-        <v>169</v>
-      </c>
-      <c r="E11">
-        <v>9.8204999999999991</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11">
-        <v>0.15759999999999999</v>
-      </c>
-      <c r="I11">
-        <v>1.413</v>
-      </c>
-      <c r="J11">
-        <v>4.7999999999999996E-3</v>
-      </c>
-      <c r="K11">
-        <v>2.819</v>
-      </c>
-      <c r="L11">
-        <v>0.11360000000000001</v>
-      </c>
-      <c r="M11">
-        <v>1.5820000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="1">
-        <v>8.5619999999999997E-5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>169</v>
-      </c>
-      <c r="E12">
-        <v>18.731000000000002</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12">
-        <v>0.55589999999999995</v>
-      </c>
-      <c r="I12">
-        <v>-0.58899999999999997</v>
-      </c>
-      <c r="J12">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="K12">
-        <v>-3.508</v>
-      </c>
-      <c r="L12">
-        <v>1.9E-3</v>
-      </c>
-      <c r="M12">
-        <v>-3.1040000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13">
-        <v>0.2767</v>
-      </c>
-      <c r="D13" t="s">
-        <v>169</v>
-      </c>
-      <c r="E13">
-        <v>2.5699000000000001</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13">
-        <v>0.51400000000000001</v>
-      </c>
-      <c r="I13">
-        <v>-0.65300000000000002</v>
-      </c>
-      <c r="J13">
-        <v>0.12670000000000001</v>
-      </c>
-      <c r="K13">
-        <v>-1.5269999999999999</v>
-      </c>
-      <c r="L13">
-        <v>0.372</v>
-      </c>
-      <c r="M13">
-        <v>-0.89300000000000002</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -3851,6 +3762,7 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -3875,10 +3787,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -3904,10 +3816,10 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>169</v>
       </c>
       <c r="C2">
         <v>3.0509999999999999E-3</v>
@@ -3916,13 +3828,13 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>8.5021000000000004</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H2">
         <v>0.49630000000000002</v>
@@ -3949,246 +3861,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04DA7A65-A190-BD4C-8356-C734F10EDBD5}">
-  <dimension ref="A1:AI2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="33.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="32.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L1" t="s">
-        <v>89</v>
-      </c>
-      <c r="M1" t="s">
-        <v>90</v>
-      </c>
-      <c r="N1" t="s">
-        <v>91</v>
-      </c>
-      <c r="O1" t="s">
-        <v>92</v>
-      </c>
-      <c r="P1" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>94</v>
-      </c>
-      <c r="R1" t="s">
-        <v>95</v>
-      </c>
-      <c r="S1" t="s">
-        <v>96</v>
-      </c>
-      <c r="T1" t="s">
-        <v>97</v>
-      </c>
-      <c r="U1" t="s">
-        <v>98</v>
-      </c>
-      <c r="V1" t="s">
-        <v>99</v>
-      </c>
-      <c r="W1" t="s">
-        <v>100</v>
-      </c>
-      <c r="X1" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>102</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>109</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.1561265</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3">
-        <v>3.7141778300000001</v>
-      </c>
-      <c r="G2" s="2">
-        <v>5.964345E-69</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="3">
-        <v>307.99702967000002</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1.194192E-4</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3">
-        <v>14.80183527</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0.98031020000000002</v>
-      </c>
-      <c r="N2">
-        <v>2</v>
-      </c>
-      <c r="O2" s="3">
-        <v>3.9772479999999999E-2</v>
-      </c>
-      <c r="P2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0.76677611999999995</v>
-      </c>
-      <c r="S2" s="3">
-        <v>3.9972140000000003E-2</v>
-      </c>
-      <c r="T2" s="3">
-        <v>1.7070350000000001E-2</v>
-      </c>
-      <c r="U2" s="3">
-        <v>-0.29988136999999998</v>
-      </c>
-      <c r="V2" s="3">
-        <v>2.1984964300000001</v>
-      </c>
-      <c r="W2" s="3">
-        <v>2.5993404999999998</v>
-      </c>
-      <c r="X2" s="3">
-        <v>24.70729</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>19.805589999999999</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>20.188829999999999</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>0.95179639999999999</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>0.10712657</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>0.10877481</v>
-      </c>
-      <c r="AD2" s="3">
-        <v>-6.0545040000000001E-2</v>
-      </c>
-      <c r="AE2" s="3">
-        <v>1.6259447600000001</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>1.61385136</v>
-      </c>
-      <c r="AG2" s="3">
-        <v>161.51829000000001</v>
-      </c>
-      <c r="AH2" s="3">
-        <v>99.439700000000002</v>
-      </c>
-      <c r="AI2" s="3">
-        <v>142.31399999999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16EE86D7-237E-6347-A038-950582B4C59E}">
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62.33203125" bestFit="1" customWidth="1"/>
@@ -4203,28 +3877,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="E1" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="F1" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="G1" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="H1" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="I1" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="J1" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="K1" t="s">
         <v>5</v>
@@ -4233,7 +3907,7 @@
         <v>6</v>
       </c>
       <c r="M1" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="N1" t="s">
         <v>7</v>
@@ -4242,7 +3916,7 @@
         <v>8</v>
       </c>
       <c r="P1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="Q1" t="s">
         <v>9</v>
@@ -4251,478 +3925,547 @@
         <v>10</v>
       </c>
       <c r="S1" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D2" s="4">
+        <v>80</v>
+      </c>
+      <c r="D2" s="2">
         <v>1.9790760000000001E-82</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="3">
         <v>369.88853999999998</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="2">
         <v>4.5775959999999997E-3</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="3">
         <v>10.773160000000001</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="5">
+        <v>34</v>
+      </c>
+      <c r="K2" s="3">
         <v>0.64851674400000003</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="3">
         <v>-0.4634028</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="3">
         <v>18.37743</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="3">
         <v>2.6342758000000001E-2</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="3">
         <v>2.4828538</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="3">
         <v>13.981960000000001</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="3">
         <v>8.1911610000000006E-3</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="3">
         <v>3.0342959</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="3">
         <v>15.35371</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" s="4">
+        <v>80</v>
+      </c>
+      <c r="D3" s="2">
         <v>1.3600799999999999E-9</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="3">
         <v>36.7252267</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="2">
         <v>0.73412299999999997</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="3">
         <v>0.61815739999999997</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="5">
+        <v>34</v>
+      </c>
+      <c r="K3" s="3">
         <v>0.73808269999999998</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="3">
         <v>-0.3382867</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="3">
         <v>24.049119999999998</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="3">
         <v>0.79884730000000004</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="3">
         <v>0.25899889999999998</v>
       </c>
-      <c r="P3" s="5">
+      <c r="P3" s="3">
         <v>16.459379999999999</v>
       </c>
-      <c r="Q3" s="5">
+      <c r="Q3" s="3">
         <v>0.45448349999999998</v>
       </c>
-      <c r="R3" s="5">
+      <c r="R3" s="3">
         <v>0.76609470000000002</v>
       </c>
-      <c r="S3" s="5">
+      <c r="S3" s="3">
         <v>16.43449</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="4">
+        <v>80</v>
+      </c>
+      <c r="D4" s="2">
         <v>1.155142E-12</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>50.561062900000003</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="2">
         <v>0.66140739999999998</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="3">
         <v>0.82677069999999997</v>
       </c>
       <c r="J4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="5">
+        <v>34</v>
+      </c>
+      <c r="K4" s="3">
         <v>0.88932040000000001</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="3">
         <v>-0.14291029999999999</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="3">
         <v>9.5852070000000005</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="3">
         <v>0.49805139999999998</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="3">
         <v>0.68894610000000001</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="3">
         <v>22.024463000000001</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="3">
         <v>0.38303589999999998</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R4" s="3">
         <v>0.89001209999999997</v>
       </c>
-      <c r="S4" s="5">
+      <c r="S4" s="3">
         <v>22.123284999999999</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="4">
+        <v>80</v>
+      </c>
+      <c r="D5" s="2">
         <v>2.794803E-16</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="3">
         <v>66.942939999999993</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="2">
         <v>5.1641170000000002E-3</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="3">
         <v>10.53204</v>
       </c>
       <c r="J5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="5">
+        <v>34</v>
+      </c>
+      <c r="K5" s="3">
         <v>0.563025212</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="3">
         <v>-0.58758129999999997</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="3">
         <v>21.182880000000001</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5" s="3">
         <v>4.7243581999999999E-2</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="3">
         <v>2.1872688</v>
       </c>
-      <c r="P5" s="5">
+      <c r="P5" s="3">
         <v>13.23668</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q5" s="3">
         <v>9.8620080000000002E-3</v>
       </c>
-      <c r="R5" s="5">
+      <c r="R5" s="3">
         <v>2.9928593999999999</v>
       </c>
-      <c r="S5" s="5">
+      <c r="S5" s="3">
         <v>13.731170000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="4">
+        <v>80</v>
+      </c>
+      <c r="D6" s="2">
         <v>1.4449549999999999E-21</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="3">
         <v>90.988692999999998</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="2">
         <v>0.61907489999999998</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="3">
         <v>0.95905799999999997</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="5">
+        <v>34</v>
+      </c>
+      <c r="K6" s="3">
         <v>0.37144470000000002</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="3">
         <v>0.91001659999999995</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="3">
         <v>25.175059999999998</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="3">
         <v>0.80790620000000002</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="3">
         <v>0.24821380000000001</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="3">
         <v>12.801270000000001</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="3">
         <v>0.40959640000000003</v>
       </c>
-      <c r="R6" s="5">
+      <c r="R6" s="3">
         <v>-0.84411060000000004</v>
       </c>
-      <c r="S6" s="5">
+      <c r="S6" s="3">
         <v>18.149349999999998</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="4">
+        <v>80</v>
+      </c>
+      <c r="D7" s="2">
         <v>6.8635909999999998E-8</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="3">
         <v>29.102851000000001</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="2">
         <v>0.22289139999999999</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="3">
         <v>3.0021420000000001</v>
       </c>
       <c r="J7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="5">
+        <v>34</v>
+      </c>
+      <c r="K7" s="3">
         <v>0.46404669999999998</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="3">
         <v>0.73824480000000003</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="3">
         <v>46.86459</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="3">
         <v>0.1148305</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="3">
         <v>1.6350547</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P7" s="3">
         <v>24.484529999999999</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q7" s="3">
         <v>0.40421879999999999</v>
       </c>
-      <c r="R7" s="5">
+      <c r="R7" s="3">
         <v>0.8516745</v>
       </c>
-      <c r="S7" s="5">
+      <c r="S7" s="3">
         <v>20.533329999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A173C1-932E-F04E-924D-93C04F4A9641}">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2">
         <v>1.075E-3</v>
       </c>
-      <c r="H8">
+      <c r="H2">
         <v>2</v>
       </c>
-      <c r="I8">
+      <c r="I2">
         <v>10.8</v>
       </c>
-      <c r="J8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8">
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2">
         <v>3.3E-3</v>
       </c>
-      <c r="L8">
+      <c r="L2">
         <v>-3.4550000000000001</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M2" s="3">
         <v>16</v>
       </c>
-      <c r="N8">
+      <c r="N2">
         <v>0.39979999999999999</v>
       </c>
-      <c r="O8">
+      <c r="O2">
         <v>0.86499999999999999</v>
       </c>
-      <c r="P8" s="5">
+      <c r="P2" s="3">
         <v>16</v>
       </c>
-      <c r="Q8">
+      <c r="Q2">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="R8">
+      <c r="R2">
         <v>4.3520000000000003</v>
       </c>
-      <c r="S8" s="5">
+      <c r="S2" s="3">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3">
         <v>1.366E-2</v>
       </c>
-      <c r="H9">
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="I9">
+      <c r="I3">
         <v>5.6825000000000001</v>
       </c>
-      <c r="J9" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9">
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="L9">
+      <c r="L3">
         <v>-3.1819999999999999</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M3" s="3">
         <v>16</v>
       </c>
-      <c r="N9">
+      <c r="N3">
         <v>0.49359999999999998</v>
       </c>
-      <c r="O9">
+      <c r="O3">
         <v>-0.70099999999999996</v>
       </c>
-      <c r="P9">
+      <c r="P3">
         <v>16</v>
       </c>
-      <c r="Q9">
+      <c r="Q3">
         <v>2.5899999999999999E-2</v>
       </c>
-      <c r="R9">
+      <c r="R3">
         <v>2.4550000000000001</v>
       </c>
-      <c r="S9" s="5">
+      <c r="S3" s="3">
         <v>16</v>
       </c>
     </row>
@@ -4744,19 +4487,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="E1" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="F1" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="G1" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
@@ -4765,7 +4508,7 @@
         <v>6</v>
       </c>
       <c r="J1" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="K1" t="s">
         <v>7</v>
@@ -4774,7 +4517,7 @@
         <v>8</v>
       </c>
       <c r="M1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="N1" t="s">
         <v>9</v>
@@ -4783,18 +4526,18 @@
         <v>10</v>
       </c>
       <c r="P1" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2">
         <v>2.581E-2</v>
@@ -4806,7 +4549,7 @@
         <v>4.6359000000000004</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H2">
         <v>0.25619999999999998</v>
@@ -4838,13 +4581,13 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>0.2356</v>
@@ -4856,7 +4599,7 @@
         <v>1.5843</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H3">
         <v>0.24329999999999999</v>
@@ -4888,13 +4631,13 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4">
         <v>2.6710000000000001E-2</v>
@@ -4906,7 +4649,7 @@
         <v>4.5823999999999998</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H4">
         <v>0.30959999999999999</v>
@@ -4957,16 +4700,16 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G1" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
@@ -4990,102 +4733,102 @@
         <v>10</v>
       </c>
       <c r="O1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" t="s">
         <v>43</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>45</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>46</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>47</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>48</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>49</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>50</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>51</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>52</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>53</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>54</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>55</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>56</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>57</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>58</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>59</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>60</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>61</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>62</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>63</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>64</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>65</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>66</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>67</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>68</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>69</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>70</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>4.1158402121135699E-4</v>
@@ -5097,31 +4840,31 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2">
         <v>9.4671958181729998</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O2">
         <v>1.1143745661520801E-3</v>
@@ -5216,10 +4959,10 @@
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>5.2701369163501103E-3</v>
@@ -5231,31 +4974,31 @@
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3">
         <v>5.4935525993957297</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O3">
         <v>6.5276537657316704E-3</v>
@@ -5350,10 +5093,10 @@
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C4" s="1">
         <v>4.4821932936411798E-15</v>
@@ -5365,31 +5108,31 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <v>169.415612662504</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O4">
         <v>6.9494386341206402E-4</v>
@@ -5410,10 +5153,10 @@
         <v>-0.693999659320653</v>
       </c>
       <c r="U4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="V4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="W4">
         <v>0.100277704633547</v>
@@ -5434,10 +5177,10 @@
         <v>-3.3891530465381399</v>
       </c>
       <c r="AC4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AD4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AE4">
         <v>1.35914060973043E-3</v>
@@ -5452,10 +5195,10 @@
         <v>-21.211741867318501</v>
       </c>
       <c r="AI4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AJ4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AK4" s="1">
         <v>1.4805205232374E-13</v>
@@ -5464,10 +5207,10 @@
         <v>-18.372970326581498</v>
       </c>
       <c r="AM4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AN4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AO4">
         <v>0.305256337112774</v>
@@ -5476,18 +5219,18 @@
         <v>-1.05365561639442</v>
       </c>
       <c r="AQ4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AR4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5">
         <v>8.2120246576537301E-3</v>
@@ -5499,31 +5242,31 @@
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5">
         <v>4.3600849090304896</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O5">
         <v>2.9336497305890098E-3</v>
@@ -5544,10 +5287,10 @@
         <v>1.71026022813958</v>
       </c>
       <c r="U5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="V5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="W5">
         <v>0.601263810191207</v>
@@ -5568,10 +5311,10 @@
         <v>-0.56343557215614004</v>
       </c>
       <c r="AC5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AD5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AE5">
         <v>0.25497196253486498</v>
@@ -5586,10 +5329,10 @@
         <v>2.5841820457954698</v>
       </c>
       <c r="AI5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AJ5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AK5">
         <v>0.16220121416527</v>
@@ -5598,10 +5341,10 @@
         <v>1.45423772065548</v>
       </c>
       <c r="AM5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AN5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AO5">
         <v>0.519854807347646</v>
@@ -5610,18 +5353,18 @@
         <v>-0.65573808423134405</v>
       </c>
       <c r="AQ5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AR5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" s="1">
         <v>1.9459358610096001E-6</v>
@@ -5633,13 +5376,13 @@
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6">
         <v>11.832897827418799</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I6">
         <v>1.02230764149151E-2</v>
@@ -5648,16 +5391,16 @@
         <v>-2.7874313623863398</v>
       </c>
       <c r="K6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O6">
         <v>1.1964985523256E-3</v>
@@ -5752,10 +5495,10 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" s="1">
         <v>7.94180654788312E-6</v>
@@ -5767,13 +5510,13 @@
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7">
         <v>10.045924793091</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I7">
         <v>2.6693272782748099E-3</v>
@@ -5782,16 +5525,16 @@
         <v>-3.3493872960395801</v>
       </c>
       <c r="K7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O7">
         <v>2.1720865412500401E-4</v>
@@ -5886,7 +5629,7 @@
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.2">
       <c r="I16" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -5901,58 +5644,58 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="B1" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E1" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="H1" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="I1" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="J1" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="K1" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="L1" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="M1" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="N1" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="O1" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="P1" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="Q1" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="R1" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="S1" t="s">
         <v>5</v>
@@ -5964,12 +5707,12 @@
         <v>9</v>
       </c>
       <c r="V1" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5978,13 +5721,13 @@
         <v>1.12863686955326E-5</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>-1.03973661509525E-2</v>
@@ -6005,13 +5748,13 @@
         <v>3.6178842477852698E-2</v>
       </c>
       <c r="M2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P2">
         <v>-0.280529869166604</v>
@@ -6037,7 +5780,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -6046,13 +5789,13 @@
         <v>9.5618423003005501E-4</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>-0.152544832589047</v>
@@ -6073,13 +5816,13 @@
         <v>4.72356015307464E-2</v>
       </c>
       <c r="M3" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N3" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O3" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P3">
         <v>-3.0821574171464601</v>
@@ -6105,7 +5848,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -6114,13 +5857,13 @@
         <v>9.6096084491155598E-15</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>-0.20482322128597799</v>
@@ -6141,13 +5884,13 @@
         <v>5.1734572273084499E-2</v>
       </c>
       <c r="M4" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N4" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O4" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P4">
         <v>-3.4597890957971198</v>
@@ -6173,7 +5916,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -6182,13 +5925,13 @@
         <v>1.50417328169436E-2</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>9.6319650098454695E-2</v>
@@ -6209,13 +5952,13 @@
         <v>5.9241435887083797E-2</v>
       </c>
       <c r="M5" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N5" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O5" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P5">
         <v>1.61186440842281</v>
@@ -6241,7 +5984,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -6250,13 +5993,13 @@
         <v>5.36101781249523E-3</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>0.17658773621142401</v>
@@ -6277,13 +6020,13 @@
         <v>6.4256558945816694E-2</v>
       </c>
       <c r="M6" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N6" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O6" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P6">
         <v>2.6348200356954301</v>
@@ -6309,7 +6052,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -6318,13 +6061,13 @@
         <v>0.42629084471082401</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>9.1082615381406204E-2</v>
@@ -6345,13 +6088,13 @@
         <v>7.0227201165208405E-2</v>
       </c>
       <c r="M7" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N7" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O7" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P7">
         <v>1.2480074406793</v>
@@ -6377,7 +6120,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -6386,13 +6129,13 @@
         <v>6.1529295060562601E-2</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>3.7676135075358002E-4</v>
@@ -6413,13 +6156,13 @@
         <v>7.2707617991221996E-2</v>
       </c>
       <c r="M8" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N8" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O8" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P8">
         <v>4.8051718864971201E-3</v>
@@ -6445,7 +6188,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -6454,13 +6197,13 @@
         <v>7.2406354551055395E-11</v>
       </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>0.18811813240683201</v>
@@ -6481,13 +6224,13 @@
         <v>7.5168908582520594E-2</v>
       </c>
       <c r="M9" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N9" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O9" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P9">
         <v>2.2748445089364502</v>
@@ -6513,7 +6256,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -6522,13 +6265,13 @@
         <v>0.266226066813537</v>
       </c>
       <c r="D10" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>3.76761347179239E-4</v>
@@ -6549,13 +6292,13 @@
         <v>7.33619267212062E-2</v>
       </c>
       <c r="M10" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N10" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O10" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P10">
         <v>4.8051748076923702E-3</v>
@@ -6581,7 +6324,7 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B11">
         <v>9</v>
@@ -6590,13 +6333,13 @@
         <v>3.1066297298011002E-5</v>
       </c>
       <c r="D11" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>0.113046197993918</v>
@@ -6617,13 +6360,13 @@
         <v>8.3283541495639601E-2</v>
       </c>
       <c r="M11" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P11">
         <v>1.4128726229499</v>
@@ -6649,7 +6392,7 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -6658,13 +6401,13 @@
         <v>8.7916239851045297E-2</v>
       </c>
       <c r="D12" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>0.169343131460194</v>
@@ -6685,13 +6428,13 @@
         <v>8.0354933038084594E-2</v>
       </c>
       <c r="M12" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N12" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O12" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P12">
         <v>2.0325078790910101</v>
@@ -6717,7 +6460,7 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B13">
         <v>11</v>
@@ -6726,13 +6469,13 @@
         <v>7.8384712635022995E-3</v>
       </c>
       <c r="D13" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>-0.18581744160157401</v>
@@ -6753,13 +6496,13 @@
         <v>8.0001499294562406E-2</v>
       </c>
       <c r="M13" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N13" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O13" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P13">
         <v>-2.0847770206244398</v>
@@ -6785,7 +6528,7 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B14">
         <v>12</v>
@@ -6794,13 +6537,13 @@
         <v>2.1287953145502001E-2</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>0.248120639806543</v>
@@ -6821,13 +6564,13 @@
         <v>8.91454086073626E-2</v>
       </c>
       <c r="M14" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N14" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O14" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P14">
         <v>2.7523098745635499</v>
@@ -6853,7 +6596,7 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B15">
         <v>13</v>
@@ -6862,13 +6605,13 @@
         <v>0.52133971844972504</v>
       </c>
       <c r="D15" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>1.88928115158527E-2</v>
@@ -6889,13 +6632,13 @@
         <v>8.6623735822233705E-2</v>
       </c>
       <c r="M15" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N15" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O15" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P15">
         <v>0.21297982040872601</v>
@@ -6921,7 +6664,7 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B16">
         <v>14</v>
@@ -6930,13 +6673,13 @@
         <v>2.5243552388971999E-2</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>-0.28486519279378397</v>
@@ -6957,13 +6700,13 @@
         <v>9.6893114973608502E-2</v>
       </c>
       <c r="M16" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N16" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O16" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P16">
         <v>-2.66343679893953</v>
@@ -6989,7 +6732,7 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B17">
         <v>15</v>
@@ -6998,13 +6741,13 @@
         <v>0.41323022250320401</v>
       </c>
       <c r="D17" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>-3.9599572971582397E-2</v>
@@ -7025,13 +6768,13 @@
         <v>0.10456625303546201</v>
       </c>
       <c r="M17" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N17" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O17" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P17">
         <v>-0.36990911297895002</v>
@@ -7057,7 +6800,7 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B18">
         <v>16</v>
@@ -7066,13 +6809,13 @@
         <v>0.87517488661672405</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18">
         <v>1.8089338572975299E-2</v>
@@ -7093,13 +6836,13 @@
         <v>0.102935347743391</v>
       </c>
       <c r="M18" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N18" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O18" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P18">
         <v>0.17005826001355401</v>
@@ -7125,7 +6868,7 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B19">
         <v>17</v>
@@ -7134,13 +6877,13 @@
         <v>6.4481197075701602E-2</v>
       </c>
       <c r="D19" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>-0.240888998806736</v>
@@ -7161,13 +6904,13 @@
         <v>0.10082074681702601</v>
       </c>
       <c r="M19" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N19" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O19" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P19">
         <v>-2.23233853952414</v>
@@ -7193,7 +6936,7 @@
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B20">
         <v>18</v>
@@ -7202,13 +6945,13 @@
         <v>7.1294259519617195E-2</v>
       </c>
       <c r="D20" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>-0.205849337068539</v>
@@ -7229,13 +6972,13 @@
         <v>0.10492238960768201</v>
       </c>
       <c r="M20" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N20" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O20" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P20">
         <v>-1.76169417350311</v>
@@ -7261,7 +7004,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B21">
         <v>19</v>
@@ -7270,13 +7013,13 @@
         <v>1.52783859227268E-2</v>
       </c>
       <c r="D21" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G21">
         <v>0.27820389163746401</v>
@@ -7297,13 +7040,13 @@
         <v>0.112962488318281</v>
       </c>
       <c r="M21" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N21" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O21" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P21">
         <v>2.3594608789039002</v>
@@ -7329,7 +7072,7 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B22">
         <v>20</v>
@@ -7338,13 +7081,13 @@
         <v>0.47105662191152903</v>
       </c>
       <c r="D22" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22">
         <v>-0.16290651292601499</v>
@@ -7365,13 +7108,13 @@
         <v>0.124435005152394</v>
       </c>
       <c r="M22" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N22" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O22" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P22">
         <v>-1.22276270969637</v>
@@ -7397,7 +7140,7 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B23">
         <v>21</v>
@@ -7406,13 +7149,13 @@
         <v>0.23651324913632699</v>
       </c>
       <c r="D23" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G23">
         <v>-0.117321933188792</v>
@@ -7433,13 +7176,13 @@
         <v>0.133100279153336</v>
       </c>
       <c r="M23" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N23" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O23" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P23">
         <v>-0.86344449335002005</v>
@@ -7465,7 +7208,7 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B24">
         <v>22</v>
@@ -7474,13 +7217,13 @@
         <v>2.6579680982606701E-3</v>
       </c>
       <c r="D24" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>-5.9435850219876699E-2</v>
@@ -7501,13 +7244,13 @@
         <v>0.14758159568350401</v>
       </c>
       <c r="M24" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N24" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O24" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P24">
         <v>-0.475783488006287</v>
@@ -7533,7 +7276,7 @@
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B25">
         <v>23</v>
@@ -7542,13 +7285,13 @@
         <v>0.168222235737084</v>
       </c>
       <c r="D25" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>0.28503220901350301</v>
@@ -7569,13 +7312,13 @@
         <v>0.15024993811311901</v>
       </c>
       <c r="M25" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N25" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O25" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P25">
         <v>1.8799749448648</v>
@@ -7601,7 +7344,7 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B26">
         <v>24</v>
@@ -7610,13 +7353,13 @@
         <v>8.5080504666461905E-5</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>-0.12715087187190299</v>
@@ -7637,13 +7380,13 @@
         <v>0.16333173612822399</v>
       </c>
       <c r="M26" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N26" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O26" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P26">
         <v>-0.86124091480477305</v>
@@ -7669,7 +7412,7 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B27">
         <v>25</v>
@@ -7678,13 +7421,13 @@
         <v>0.28593643351173498</v>
       </c>
       <c r="D27" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>0.19593839146746</v>
@@ -7705,13 +7448,13 @@
         <v>0.191266955136493</v>
       </c>
       <c r="M27" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N27" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O27" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P27">
         <v>1.0492140347271099</v>
@@ -7737,7 +7480,7 @@
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B28">
         <v>26</v>
@@ -7746,13 +7489,13 @@
         <v>4.0039233790885802E-2</v>
       </c>
       <c r="D28" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>-0.48112654637810298</v>
@@ -7773,13 +7516,13 @@
         <v>0.41312934183702599</v>
       </c>
       <c r="M28" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N28" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O28" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P28">
         <v>-1.2148846185263</v>
@@ -7805,7 +7548,7 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -7814,13 +7557,13 @@
         <v>2.99276870725992E-5</v>
       </c>
       <c r="D30" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E30">
         <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <v>-8.0863078772300603E-2</v>
@@ -7841,13 +7584,13 @@
         <v>3.8081271686453699E-2</v>
       </c>
       <c r="M30" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N30" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O30" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P30">
         <v>-2.0749823436714698</v>
@@ -7873,7 +7616,7 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B31">
         <v>3</v>
@@ -7882,13 +7625,13 @@
         <v>0.112456303274495</v>
       </c>
       <c r="D31" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G31">
         <v>4.4143234582122E-2</v>
@@ -7909,13 +7652,13 @@
         <v>6.0046952104135499E-2</v>
       </c>
       <c r="M31" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N31" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O31" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P31">
         <v>0.72885294941953405</v>
@@ -7941,7 +7684,7 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B32">
         <v>4</v>
@@ -7950,13 +7693,13 @@
         <v>5.9137713450477698E-3</v>
       </c>
       <c r="D32" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G32">
         <v>0.13805332715354701</v>
@@ -7977,13 +7720,13 @@
         <v>6.5009832110026894E-2</v>
       </c>
       <c r="M32" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N32" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O32" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P32">
         <v>2.0379064808271998</v>
@@ -8009,7 +7752,7 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B33">
         <v>5</v>
@@ -8018,13 +7761,13 @@
         <v>0.63674742126525796</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G33">
         <v>3.97171162050447E-2</v>
@@ -8045,13 +7788,13 @@
         <v>7.0875736649364598E-2</v>
       </c>
       <c r="M33" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N33" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O33" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P33">
         <v>0.53957693251830596</v>
@@ -8077,7 +7820,7 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B34">
         <v>6</v>
@@ -8086,13 +7829,13 @@
         <v>1.8031089361808299E-2</v>
       </c>
       <c r="D34" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G34">
         <v>-5.2082655018378901E-2</v>
@@ -8113,13 +7856,13 @@
         <v>7.3329653542656498E-2</v>
       </c>
       <c r="M34" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N34" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O34" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P34">
         <v>-0.65943032475561203</v>
@@ -8145,7 +7888,7 @@
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B35">
         <v>7</v>
@@ -8154,13 +7897,13 @@
         <v>1.37194697287356E-11</v>
       </c>
       <c r="D35" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G35">
         <v>0.138412650045144</v>
@@ -8181,13 +7924,13 @@
         <v>7.5769845867899893E-2</v>
       </c>
       <c r="M35" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N35" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O35" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P35">
         <v>1.66293573059677</v>
@@ -8213,7 +7956,7 @@
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B36">
         <v>8</v>
@@ -8222,13 +7965,13 @@
         <v>0.106447619571215</v>
       </c>
       <c r="D36" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G36">
         <v>-5.2082655019097E-2</v>
@@ -8249,13 +7992,13 @@
         <v>7.3977153011503594E-2</v>
       </c>
       <c r="M36" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N36" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O36" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P36">
         <v>-0.65943049706349599</v>
@@ -8281,7 +8024,7 @@
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B37">
         <v>9</v>
@@ -8290,13 +8033,13 @@
         <v>2.22518178073571E-4</v>
       </c>
       <c r="D37" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G37">
         <v>6.2289308915806897E-2</v>
@@ -8317,13 +8060,13 @@
         <v>8.38141065928696E-2</v>
       </c>
       <c r="M37" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N37" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O37" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P37">
         <v>0.77309188784817395</v>
@@ -8349,7 +8092,7 @@
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B38">
         <v>10</v>
@@ -8358,13 +8101,13 @@
         <v>0.17612014721017599</v>
       </c>
       <c r="D38" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38">
         <v>0.119395833773419</v>
@@ -8385,13 +8128,13 @@
         <v>8.0907456854037996E-2</v>
       </c>
       <c r="M38" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N38" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O38" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P38">
         <v>1.4238968516842201</v>
@@ -8417,7 +8160,7 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B39">
         <v>12</v>
@@ -8426,13 +8169,13 @@
         <v>8.8746471994196996E-2</v>
       </c>
       <c r="D39" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E39">
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G39">
         <v>0.19906384728844001</v>
@@ -8453,13 +8196,13 @@
         <v>8.9635861344477596E-2</v>
       </c>
       <c r="M39" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N39" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O39" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P39">
         <v>2.1962535154559002</v>
@@ -8485,7 +8228,7 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B40">
         <v>14</v>
@@ -8494,13 +8237,13 @@
         <v>5.1536276739961896E-3</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G40">
         <v>-0.33823244588065599</v>
@@ -8521,13 +8264,13 @@
         <v>9.7339496241237194E-2</v>
       </c>
       <c r="M40" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N40" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O40" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P40">
         <v>-3.1505241520344098</v>
@@ -8553,7 +8296,7 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B41">
         <v>16</v>
@@ -8562,13 +8305,13 @@
         <v>0.92851820472353896</v>
       </c>
       <c r="D41" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G41">
         <v>-3.2924622119086297E-2</v>
@@ -8589,13 +8332,13 @@
         <v>0.103353230973558</v>
       </c>
       <c r="M41" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N41" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O41" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P41">
         <v>-0.30834949173988901</v>
@@ -8621,7 +8364,7 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B42">
         <v>17</v>
@@ -8630,13 +8373,13 @@
         <v>2.2233468020057299E-2</v>
       </c>
       <c r="D42" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E42">
         <v>2</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G42">
         <v>-0.29383908357274602</v>
@@ -8657,13 +8400,13 @@
         <v>0.10124844775956</v>
       </c>
       <c r="M42" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N42" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O42" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P42">
         <v>-2.7129801854679201</v>
@@ -8689,7 +8432,7 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B43">
         <v>18</v>
@@ -8698,13 +8441,13 @@
         <v>1.97768942022182E-2</v>
       </c>
       <c r="D43" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G43">
         <v>-0.25807317688577203</v>
@@ -8725,13 +8468,13 @@
         <v>0.105331640749825</v>
       </c>
       <c r="M43" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N43" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O43" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P43">
         <v>-2.2017288190918398</v>
@@ -8757,7 +8500,7 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B44">
         <v>19</v>
@@ -8766,13 +8509,13 @@
         <v>2.44066184245227E-2</v>
       </c>
       <c r="D44" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E44">
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G44">
         <v>0.22904258377464501</v>
@@ -8793,13 +8536,13 @@
         <v>0.113340751839626</v>
       </c>
       <c r="M44" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N44" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O44" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P44">
         <v>1.9365615537238301</v>
@@ -8825,7 +8568,7 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B45">
         <v>21</v>
@@ -8834,13 +8577,13 @@
         <v>0.20745166977972401</v>
       </c>
       <c r="D45" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E45">
         <v>2</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G45">
         <v>-0.16845426123986901</v>
@@ -8861,13 +8604,13 @@
         <v>0.13341792149079501</v>
       </c>
       <c r="M45" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N45" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O45" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P45">
         <v>-1.23691817001724</v>
@@ -8893,7 +8636,7 @@
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B46">
         <v>22</v>
@@ -8902,13 +8645,13 @@
         <v>3.4294369676319599E-3</v>
       </c>
       <c r="D46" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E46">
         <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G46">
         <v>-0.110511365115966</v>
@@ -8929,13 +8672,13 @@
         <v>0.14792070660425199</v>
       </c>
       <c r="M46" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N46" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O46" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P46">
         <v>-0.88223531702442903</v>
@@ -8961,7 +8704,7 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B47">
         <v>23</v>
@@ -8970,13 +8713,13 @@
         <v>0.29599129516915701</v>
       </c>
       <c r="D47" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
       <c r="F47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G47">
         <v>0.23566583476476899</v>
@@ -8997,13 +8740,13 @@
         <v>0.15052943447265801</v>
       </c>
       <c r="M47" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N47" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O47" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P47">
         <v>1.55152596489022</v>
@@ -9029,7 +8772,7 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B48">
         <v>24</v>
@@ -9038,13 +8781,13 @@
         <v>1.1522866033545099E-4</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E48">
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G48">
         <v>-0.17810247100160101</v>
@@ -9065,13 +8808,13 @@
         <v>0.16358865527871699</v>
       </c>
       <c r="M48" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N48" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O48" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P48">
         <v>-1.2040266497013601</v>
@@ -9097,7 +8840,7 @@
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="B49">
         <v>25</v>
@@ -9106,13 +8849,13 @@
         <v>0.42678208751226698</v>
       </c>
       <c r="D49" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="E49">
         <v>2</v>
       </c>
       <c r="F49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G49">
         <v>0.14623119053474101</v>
@@ -9133,13 +8876,13 @@
         <v>0.19148451587349</v>
       </c>
       <c r="M49" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="N49" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="O49" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="P49">
         <v>0.782104079097245</v>
